--- a/results/CB/ActualCorrections.xlsx
+++ b/results/CB/ActualCorrections.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S386"/>
+  <dimension ref="A1:S383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>, 9.35</t>
+          <t>GO, 9.35</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>, 8.95</t>
+          <t>GO, 8.95</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>, 9.09</t>
+          <t>GO, 9.09</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>, 9.13</t>
+          <t>GO, 9.13</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -10014,14 +10014,12 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
+      <c r="G108" t="n">
+        <v>30</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10046,7 +10044,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -10059,7 +10057,11 @@
           <t>ResponseTime</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="Q108" t="inlineStr">
         <is>
           <t>NULL</t>
@@ -11473,7 +11475,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11498,7 +11500,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>, 10.93</t>
+          <t>GO, 10.93</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -27481,7 +27483,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
@@ -27568,7 +27570,7 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
@@ -27655,7 +27657,7 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
@@ -28633,7 +28635,7 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28641,16 +28643,16 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>9.35</v>
+        <v>9.09</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>No button press- resp is criterion</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
@@ -28670,7 +28672,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>, 9.35</t>
+          <t>GO, 9.09</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -28683,10 +28685,14 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P314" t="inlineStr"/>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="Q314" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -28720,7 +28726,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28728,11 +28734,11 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>8.949999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -28757,7 +28763,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>, 8.95</t>
+          <t>GO, 9.13</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -28770,10 +28776,14 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P315" t="inlineStr"/>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -28803,11 +28813,11 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>dusty</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28815,21 +28825,21 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>9.09</v>
+        <v>12.4</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Early horse release before button not pressed</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
+          <t>Experiment_2023-11-14T12:13:40.543722_dusty_6.0_Training randomised Type 1.log</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -28844,7 +28854,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>, 9.09</t>
+          <t>GO, 12.4</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -28857,7 +28867,11 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P316" t="inlineStr"/>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="Q316" t="inlineStr">
         <is>
           <t>NOGO</t>
@@ -28881,11 +28895,11 @@
         </is>
       </c>
       <c r="B317" s="2" t="n">
-        <v>45248</v>
+        <v>45249</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBT1</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -28894,29 +28908,29 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>9.130000000000001</v>
+        <v>7.83</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Go response triggered but Not registered</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
+          <t>Experiment_2023-11-14T12:37:30.469954_gio_5.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -28931,7 +28945,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>, 9.13</t>
+          <t>GO, 7.83</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -28944,7 +28958,11 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P317" t="inlineStr"/>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="Q317" t="inlineStr">
         <is>
           <t>NOGO</t>
@@ -28968,7 +28986,7 @@
         </is>
       </c>
       <c r="B318" s="2" t="n">
-        <v>45248</v>
+        <v>45249</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -28977,11 +28995,11 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>dusty</t>
+          <t>pumba</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -28989,7 +29007,7 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>12.4</v>
+        <v>12.04</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
@@ -28998,12 +29016,12 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>Early horse release before button not pressed</t>
+          <t>NoGo response when should be Go response- no button press</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T12:13:40.543722_dusty_6.0_Training randomised Type 1.log</t>
+          <t>Experiment_2023-11-14T15:40:26.284336_pumba_nan_Training randomised Type 2.log</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -29018,7 +29036,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>GO, 12.4</t>
+          <t>GO, 12.04</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -29059,28 +29077,28 @@
         </is>
       </c>
       <c r="B319" s="2" t="n">
-        <v>45249</v>
+        <v>45250</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBR3</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G319" t="n">
-        <v>7.83</v>
+        <v>9.68</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
@@ -29089,12 +29107,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>Go response triggered but Not registered</t>
+          <t>Was neg. but bucket was positive-check vid- Go response</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T12:37:30.469954_gio_5.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-14T19:16:58.918521_yoshi_6.0_Training randomised Type 1.log</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -29109,7 +29127,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>GO, 7.83</t>
+          <t>GO, 9.68</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -29150,28 +29168,28 @@
         </is>
       </c>
       <c r="B320" s="2" t="n">
-        <v>45249</v>
+        <v>45251</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBT2</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>pumba</t>
+          <t>george</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>12.04</v>
+        <v>15.45</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
@@ -29180,12 +29198,12 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>NoGo response when should be Go response- no button press</t>
+          <t>Late button press for GO</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T15:40:26.284336_pumba_nan_Training randomised Type 2.log</t>
+          <t>Experiment_2023-11-15T02:59:50.231712_george_6.0_Test Type 2.log</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -29200,7 +29218,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>GO, 12.04</t>
+          <t>GO, 15.45</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -29241,44 +29259,42 @@
         </is>
       </c>
       <c r="B321" s="2" t="n">
-        <v>45250</v>
+        <v>45251</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBT2</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>jelly</t>
+          <t>nix</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>24.2</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>NoGo response but ate from bucket</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T17:14:25.139579_jelly_6.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -29293,7 +29309,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>GO, 24.2</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -29306,7 +29322,11 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P321" t="inlineStr"/>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="Q321" t="inlineStr">
         <is>
           <t>NOGO</t>
@@ -29330,16 +29350,16 @@
         </is>
       </c>
       <c r="B322" s="2" t="n">
-        <v>45250</v>
+        <v>45252</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>CBR3</t>
+          <t>CBT2</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>smudge</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -29351,7 +29371,7 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>9.68</v>
+        <v>29.46</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
@@ -29360,12 +29380,12 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>Was neg. but bucket was positive-check vid- Go response</t>
+          <t>Just timed out on Neg bucket for NoGo- check vid</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T19:16:58.918521_yoshi_6.0_Training randomised Type 1.log</t>
+          <t>Experiment_2023-11-15T16:42:36.211643_smudge_8.0_Test Type 2.log</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -29380,7 +29400,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>GO, 9.68</t>
+          <t>GO, 29.46</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -29421,7 +29441,7 @@
         </is>
       </c>
       <c r="B323" s="2" t="n">
-        <v>45251</v>
+        <v>45253</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -29430,19 +29450,19 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>george</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G323" t="n">
-        <v>15.45</v>
+        <v>10.93</v>
       </c>
       <c r="H323" t="inlineStr">
         <is>
@@ -29451,12 +29471,12 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>Late button press for GO</t>
+          <t>Early horse release before button not pressed</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T02:59:50.231712_george_6.0_Test Type 2.log</t>
+          <t>Experiment_2023-11-15T18:35:59.371714_yoshi_9.0_Test Type 2.log</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -29471,7 +29491,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>GO, 15.45</t>
+          <t>GO, 10.93</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -29512,7 +29532,7 @@
         </is>
       </c>
       <c r="B324" s="2" t="n">
-        <v>45251</v>
+        <v>45253</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -29521,19 +29541,19 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>nix</t>
+          <t>clover</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G324" t="n">
-        <v>24.2</v>
+        <v>12.67</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -29542,12 +29562,12 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t xml:space="preserve">Was run as N, then repeated so horse did extra 11 (P). </t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -29562,7 +29582,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>GO, 24.2</t>
+          <t>GO, 12.67</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -29603,7 +29623,7 @@
         </is>
       </c>
       <c r="B325" s="2" t="n">
-        <v>45252</v>
+        <v>45253</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -29612,19 +29632,19 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>smudge</t>
+          <t>clover</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>29.46</v>
+        <v>12.8</v>
       </c>
       <c r="H325" t="inlineStr">
         <is>
@@ -29633,12 +29653,12 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>Just timed out on Neg bucket for NoGo- check vid</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T16:42:36.211643_smudge_8.0_Test Type 2.log</t>
+          <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -29653,7 +29673,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>GO, 29.46</t>
+          <t>GO, 12.8</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -29694,42 +29714,42 @@
         </is>
       </c>
       <c r="B326" s="2" t="n">
-        <v>45253</v>
+        <v>45255</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>CBT2</t>
+          <t>CBT3</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>nix</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="G326" t="n">
-        <v>10.93</v>
+        <v>30</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>Early horse release before button not pressed</t>
+          <t>Did not touch. Bucket</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T18:35:59.371714_yoshi_9.0_Test Type 2.log</t>
+          <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -29744,7 +29764,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>, 10.93</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -29757,10 +29777,14 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P326" t="inlineStr"/>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
       <c r="Q326" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -29781,24 +29805,24 @@
         </is>
       </c>
       <c r="B327" s="2" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>CBT2</t>
+          <t>CBT4</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>clover</t>
+          <t>nix</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -29811,12 +29835,12 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Was run as N, then repeated so horse did extra 11 (P). </t>
+          <t xml:space="preserve">No button press- Go resp is criterion- check vids </t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
+          <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -29872,28 +29896,28 @@
         </is>
       </c>
       <c r="B328" s="2" t="n">
-        <v>45253</v>
+        <v>45257</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>CBT2</t>
+          <t>CBT4</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>clover</t>
+          <t>jelly</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>12.8</v>
+        <v>27.17</v>
       </c>
       <c r="H328" t="inlineStr">
         <is>
@@ -29902,12 +29926,12 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t xml:space="preserve">Go response but not captured </t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
+          <t>Experiment_2023-11-16T19:24:59.492473_jelly_9.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -29922,7 +29946,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>GO, 12.8</t>
+          <t>GO, 27.17</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -29963,77 +29987,77 @@
         </is>
       </c>
       <c r="B329" s="2" t="n">
-        <v>45255</v>
+        <v>45257</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>CBT3</t>
+          <t>CBT4</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>nix</t>
+          <t>smudge</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G329" t="n">
-        <v>30</v>
+        <v>10.79</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Go response but not captured </t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>TrialCBs, ResponseCBs</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>ResponseType, ResponseTime</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>GO, 10.79</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>TrialCBs</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>ResponseType</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
           <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>Did not touch. Bucket</t>
-        </is>
-      </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
-        </is>
-      </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t>TrialCBs, ResponseCBs</t>
-        </is>
-      </c>
-      <c r="L329" t="inlineStr">
-        <is>
-          <t>ResponseType, ResponseTime</t>
-        </is>
-      </c>
-      <c r="M329" t="inlineStr">
-        <is>
-          <t>NOGO, 30</t>
-        </is>
-      </c>
-      <c r="N329" t="inlineStr">
-        <is>
-          <t>TrialCBs</t>
-        </is>
-      </c>
-      <c r="O329" t="inlineStr">
-        <is>
-          <t>ResponseType</t>
-        </is>
-      </c>
-      <c r="P329" t="inlineStr">
-        <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="Q329" t="inlineStr">
-        <is>
-          <t>GO</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -30054,7 +30078,7 @@
         </is>
       </c>
       <c r="B330" s="2" t="n">
-        <v>45256</v>
+        <v>45257</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -30063,19 +30087,19 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>nix</t>
+          <t>smudge</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G330" t="n">
-        <v>12.67</v>
+        <v>10.13</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -30084,12 +30108,12 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">No button press- Go resp is criterion- check vids </t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -30104,7 +30128,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>GO, 12.67</t>
+          <t>GO, 10.13</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -30149,24 +30173,24 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>CBT4</t>
+          <t>CBT3</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>jelly</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>27.17</v>
+        <v>10.56</v>
       </c>
       <c r="H331" t="inlineStr">
         <is>
@@ -30175,12 +30199,12 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Go response but not captured </t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T19:24:59.492473_jelly_9.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -30195,7 +30219,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>GO, 27.17</t>
+          <t>GO, 10.56</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -30240,24 +30264,24 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>CBT4</t>
+          <t>CBT3</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>smudge</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>10.79</v>
+        <v>8.6</v>
       </c>
       <c r="H332" t="inlineStr">
         <is>
@@ -30266,12 +30290,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Go response but not captured </t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -30286,7 +30310,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>GO, 10.79</t>
+          <t>GO, 8.6</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -30327,28 +30351,28 @@
         </is>
       </c>
       <c r="B333" s="2" t="n">
-        <v>45257</v>
+        <v>45248</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>CBT4</t>
+          <t>CBR2</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>smudge</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>10.13</v>
+        <v>27.2</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
@@ -30357,12 +30381,12 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NoGo response when should be Go response</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
+          <t>Experiment_2023-11-14T00:45:14.508317_myrtle_4.0_Training randomised Type 2.log</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -30377,7 +30401,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>GO, 10.13</t>
+          <t>GO, 27.2</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -30418,32 +30442,32 @@
         </is>
       </c>
       <c r="B334" s="2" t="n">
-        <v>45257</v>
+        <v>45247</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>CBT3</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>M</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>10.56</v>
+        <v>30</v>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -30453,7 +30477,7 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
+          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -30468,7 +30492,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>GO, 10.56</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -30483,12 +30507,12 @@
       </c>
       <c r="P334" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -30509,11 +30533,11 @@
         </is>
       </c>
       <c r="B335" s="2" t="n">
-        <v>45257</v>
+        <v>45247</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>CBT3</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -30522,19 +30546,19 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -30544,7 +30568,7 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
+          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -30559,27 +30583,27 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>GO, 8.6</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P335" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -30600,42 +30624,42 @@
         </is>
       </c>
       <c r="B336" s="2" t="n">
-        <v>45248</v>
+        <v>45247</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>N</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>27.2</v>
+        <v>30</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>NoGo response when should be Go response</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T00:45:14.508317_myrtle_4.0_Training randomised Type 2.log</t>
+          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -30650,7 +30674,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>GO, 27.2</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -30665,12 +30689,12 @@
       </c>
       <c r="P336" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -30704,7 +30728,7 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30746,17 +30770,17 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P337" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q337" t="inlineStr">
@@ -30795,7 +30819,7 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30837,17 +30861,17 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P338" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="Q338" t="inlineStr">
@@ -30886,7 +30910,7 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30928,17 +30952,17 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P339" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q339" t="inlineStr">
@@ -30964,24 +30988,24 @@
         </is>
       </c>
       <c r="B340" s="2" t="n">
-        <v>45247</v>
+        <v>45248</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>CBF3</t>
+          <t>CBR2</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>N</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -30999,7 +31023,7 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
+          <t>Experiment_2023-11-14T00:45:14.508317_myrtle_4.0_Training randomised Type 2.log</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -31019,17 +31043,17 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P340" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="Q340" t="inlineStr">
@@ -31055,24 +31079,24 @@
         </is>
       </c>
       <c r="B341" s="2" t="n">
-        <v>45247</v>
+        <v>45248</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>CBF3</t>
+          <t>CBR2</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>N</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -31090,7 +31114,7 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
+          <t>Experiment_2023-11-14T00:45:14.508317_myrtle_4.0_Training randomised Type 2.log</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -31110,17 +31134,17 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P341" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q341" t="inlineStr">
@@ -31159,19 +31183,19 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>P</t>
         </is>
       </c>
       <c r="G342" t="n">
-        <v>30</v>
+        <v>12.4</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -31196,22 +31220,22 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 12.4</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P342" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="Q342" t="inlineStr">
@@ -31237,32 +31261,32 @@
         </is>
       </c>
       <c r="B343" s="2" t="n">
-        <v>45248</v>
+        <v>45247</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>30</v>
+        <v>12.4</v>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -31272,7 +31296,7 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T00:45:14.508317_myrtle_4.0_Training randomised Type 2.log</t>
+          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -31287,22 +31311,22 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 12.4</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P343" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="Q343" t="inlineStr">
@@ -31328,32 +31352,32 @@
         </is>
       </c>
       <c r="B344" s="2" t="n">
-        <v>45248</v>
+        <v>45247</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>30</v>
+        <v>16.89</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -31363,7 +31387,7 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T00:45:14.508317_myrtle_4.0_Training randomised Type 2.log</t>
+          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -31378,22 +31402,22 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 16.89</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P344" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="Q344" t="inlineStr">
@@ -31432,7 +31456,7 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31440,7 +31464,7 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>12.4</v>
+        <v>16.89</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
@@ -31469,22 +31493,22 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>GO, 12.4</t>
+          <t>GO, 16.89</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P345" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="Q345" t="inlineStr">
@@ -31523,19 +31547,19 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G346" t="n">
-        <v>12.4</v>
+        <v>30</v>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -31560,22 +31584,22 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>GO, 12.4</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P346" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="Q346" t="inlineStr">
@@ -31614,19 +31638,19 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>16.89</v>
+        <v>30</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -31651,22 +31675,22 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>GO, 16.89</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P347" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q347" t="inlineStr">
@@ -31705,19 +31729,19 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>16.89</v>
+        <v>30</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -31742,22 +31766,22 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>GO, 16.89</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P348" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="Q348" t="inlineStr">
@@ -31796,7 +31820,7 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31838,17 +31862,17 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P349" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q349" t="inlineStr">
@@ -31870,46 +31894,46 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B350" s="2" t="n">
-        <v>45247</v>
+        <v>45210</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>CBF3</t>
+          <t>CBR1</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>molly</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="G350" t="n">
-        <v>30</v>
+        <v>11.08</v>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Early horse release before button not pressed</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
+          <t>Experiment_2023-10-11T09:46:53.960298_molly_8_Test Type 1.log</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -31924,22 +31948,22 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.08</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P350" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="Q350" t="inlineStr">
@@ -31961,46 +31985,46 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B351" s="2" t="n">
-        <v>45247</v>
+        <v>45210</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>CBF3</t>
+          <t>CBR1</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>molly</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="G351" t="n">
-        <v>30</v>
+        <v>11.08</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Early horse release before button not pressed</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
+          <t>Experiment_2023-10-11T09:46:53.960298_molly_8_Test Type 1.log</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
@@ -32015,22 +32039,22 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.08</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="Q351" t="inlineStr">
@@ -32069,19 +32093,19 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>P</t>
         </is>
       </c>
       <c r="G352" t="n">
-        <v>30</v>
+        <v>11.99</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -32106,22 +32130,22 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.99</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P352" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="Q352" t="inlineStr">
@@ -32143,32 +32167,32 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B353" s="2" t="n">
-        <v>45210</v>
+        <v>45247</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>CBR1</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>molly</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G353" t="n">
-        <v>11.08</v>
+        <v>11.99</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
@@ -32177,12 +32201,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>Early horse release before button not pressed</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>Experiment_2023-10-11T09:46:53.960298_molly_8_Test Type 1.log</t>
+          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -32197,22 +32221,22 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>GO, 11.08</t>
+          <t>GO, 11.99</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P353" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>11.99</t>
         </is>
       </c>
       <c r="Q353" t="inlineStr">
@@ -32234,46 +32258,46 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B354" s="2" t="n">
-        <v>45210</v>
+        <v>45247</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>CBR1</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>molly</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G354" t="n">
-        <v>11.08</v>
+        <v>30</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>Early horse release before button not pressed</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>Experiment_2023-10-11T09:46:53.960298_molly_8_Test Type 1.log</t>
+          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
@@ -32288,22 +32312,22 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>GO, 11.08</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P354" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="Q354" t="inlineStr">
@@ -32342,19 +32366,19 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G355" t="n">
-        <v>11.99</v>
+        <v>30</v>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -32379,22 +32403,22 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>GO, 11.99</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P355" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q355" t="inlineStr">
@@ -32433,7 +32457,7 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32441,7 +32465,7 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>11.99</v>
+        <v>12.67</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
@@ -32470,22 +32494,22 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>GO, 11.99</t>
+          <t>GO, 12.67</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P356" t="inlineStr">
         <is>
-          <t>11.99</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="Q356" t="inlineStr">
@@ -32524,19 +32548,19 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>P</t>
         </is>
       </c>
       <c r="G357" t="n">
-        <v>30</v>
+        <v>12.67</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -32561,22 +32585,22 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 12.67</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P357" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="Q357" t="inlineStr">
@@ -32615,19 +32639,19 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>P</t>
         </is>
       </c>
       <c r="G358" t="n">
-        <v>30</v>
+        <v>12.37</v>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -32652,22 +32676,22 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 12.37</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P358" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="Q358" t="inlineStr">
@@ -32706,7 +32730,7 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32714,7 +32738,7 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>12.67</v>
+        <v>12.37</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
@@ -32743,22 +32767,22 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>GO, 12.67</t>
+          <t>GO, 12.37</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P359" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="Q359" t="inlineStr">
@@ -32780,32 +32804,34 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B360" s="2" t="n">
-        <v>45247</v>
+        <v>45209</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>CBF3</t>
+          <t>CBT1</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>yoshi</t>
-        </is>
-      </c>
-      <c r="E360" t="n">
-        <v>2</v>
+          <t>dougie</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G360" t="n">
-        <v>12.67</v>
+        <v>11.81</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
@@ -32814,12 +32840,12 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Blue button not working-16:05:45</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
+          <t>Experiment_2023-10-10T16:00:54.429454_dougie_8_Test Type 1.log</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
@@ -32834,22 +32860,22 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>GO, 12.67</t>
+          <t>GO, 11.81</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P360" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="Q360" t="inlineStr">
@@ -32871,32 +32897,34 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B361" s="2" t="n">
-        <v>45247</v>
+        <v>45209</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>CBF3</t>
+          <t>CBT1</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>yoshi</t>
-        </is>
-      </c>
-      <c r="E361" t="n">
-        <v>7</v>
+          <t>dougie</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G361" t="n">
-        <v>12.37</v>
+        <v>11.81</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
@@ -32905,12 +32933,12 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Blue button not working-16:05:45</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
+          <t>Experiment_2023-10-10T16:00:54.429454_dougie_8_Test Type 1.log</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
@@ -32925,22 +32953,22 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>GO, 12.37</t>
+          <t>GO, 11.81</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P361" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>11.81</t>
         </is>
       </c>
       <c r="Q361" t="inlineStr">
@@ -32966,42 +32994,42 @@
         </is>
       </c>
       <c r="B362" s="2" t="n">
-        <v>45247</v>
+        <v>45248</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>CBF3</t>
+          <t>CBR2</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G362" t="n">
-        <v>12.37</v>
+        <v>30</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
+          <t>Experiment_2023-11-14T01:18:45.941991_myrtle_5.0_Training randomised Type 2.log</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
@@ -33016,22 +33044,22 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>GO, 12.37</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P362" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="Q362" t="inlineStr">
@@ -33053,48 +33081,46 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B363" s="2" t="n">
-        <v>45209</v>
+        <v>45248</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBR2</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>dougie</t>
-        </is>
-      </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
+          <t>myrtle</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>20</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>11.81</v>
+        <v>30</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>Blue button not working-16:05:45</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>Experiment_2023-10-10T16:00:54.429454_dougie_8_Test Type 1.log</t>
+          <t>Experiment_2023-11-14T01:18:45.941991_myrtle_5.0_Training randomised Type 2.log</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
@@ -33109,22 +33135,22 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>GO, 11.81</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P363" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q363" t="inlineStr">
@@ -33146,34 +33172,32 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B364" s="2" t="n">
-        <v>45209</v>
+        <v>45247</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>dougie</t>
-        </is>
-      </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
+          <t>yoshi</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>8</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>11.81</v>
+        <v>26.7</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
@@ -33182,12 +33206,12 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>Blue button not working-16:05:45</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>Experiment_2023-10-10T16:00:54.429454_dougie_8_Test Type 1.log</t>
+          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
@@ -33202,22 +33226,22 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>GO, 11.81</t>
+          <t>GO, 26.7</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P364" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="Q364" t="inlineStr">
@@ -33243,42 +33267,42 @@
         </is>
       </c>
       <c r="B365" s="2" t="n">
-        <v>45248</v>
+        <v>45247</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G365" t="n">
-        <v>30</v>
+        <v>26.7</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T01:18:45.941991_myrtle_5.0_Training randomised Type 2.log</t>
+          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
@@ -33293,22 +33317,22 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 26.7</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P365" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="Q365" t="inlineStr">
@@ -33334,24 +33358,24 @@
         </is>
       </c>
       <c r="B366" s="2" t="n">
-        <v>45248</v>
+        <v>45247</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>N</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G366" t="n">
@@ -33364,12 +33388,12 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T01:18:45.941991_myrtle_5.0_Training randomised Type 2.log</t>
+          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
@@ -33389,17 +33413,17 @@
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P366" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="Q366" t="inlineStr">
@@ -33438,19 +33462,19 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G367" t="n">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -33475,22 +33499,22 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>GO, 26.7</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P367" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q367" t="inlineStr">
@@ -33529,19 +33553,19 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G368" t="n">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -33566,22 +33590,22 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>GO, 26.7</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P368" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="Q368" t="inlineStr">
@@ -33620,7 +33644,7 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33662,17 +33686,17 @@
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P369" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q369" t="inlineStr">
@@ -33711,24 +33735,24 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>P</t>
         </is>
       </c>
       <c r="G370" t="n">
-        <v>30</v>
+        <v>11.13</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Ran CBR1 but should be CBF3- so manually check all timings</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
@@ -33748,22 +33772,22 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.13</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P370" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="Q370" t="inlineStr">
@@ -33802,24 +33826,24 @@
         </is>
       </c>
       <c r="E371" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>P</t>
         </is>
       </c>
       <c r="G371" t="n">
-        <v>30</v>
+        <v>11.13</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Ran CBR1 but should be CBF3- so manually check all timings</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
@@ -33839,22 +33863,22 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.13</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P371" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>11.13</t>
         </is>
       </c>
       <c r="Q371" t="inlineStr">
@@ -33880,16 +33904,16 @@
         </is>
       </c>
       <c r="B372" s="2" t="n">
-        <v>45247</v>
+        <v>45248</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>CBF3</t>
+          <t>CBR2</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E372" t="n">
@@ -33897,25 +33921,25 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t xml:space="preserve">N </t>
+          <t>P</t>
         </is>
       </c>
       <c r="G372" t="n">
-        <v>30</v>
+        <v>11.66</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>20 s</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
+          <t>Experiment_2023-11-14T00:45:14.508317_myrtle_4.0_Training randomised Type 2.log</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
@@ -33930,22 +33954,22 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>NOGO, 30</t>
+          <t>GO, 11.66</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P372" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="Q372" t="inlineStr">
@@ -33971,20 +33995,20 @@
         </is>
       </c>
       <c r="B373" s="2" t="n">
-        <v>45247</v>
+        <v>45248</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>CBF3</t>
+          <t>CBR2</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33992,7 +34016,7 @@
         </is>
       </c>
       <c r="G373" t="n">
-        <v>11.13</v>
+        <v>11.66</v>
       </c>
       <c r="H373" t="inlineStr">
         <is>
@@ -34001,12 +34025,12 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>Ran CBR1 but should be CBF3- so manually check all timings</t>
+          <t>20 s</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
+          <t>Experiment_2023-11-14T00:45:14.508317_myrtle_4.0_Training randomised Type 2.log</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
@@ -34021,22 +34045,22 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>GO, 11.13</t>
+          <t>GO, 11.66</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P373" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="Q373" t="inlineStr">
@@ -34075,7 +34099,7 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34083,7 +34107,7 @@
         </is>
       </c>
       <c r="G374" t="n">
-        <v>11.13</v>
+        <v>14</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
@@ -34092,7 +34116,7 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>Ran CBR1 but should be CBF3- so manually check all timings</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
@@ -34112,22 +34136,22 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>GO, 11.13</t>
+          <t>GO, 14</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P374" t="inlineStr">
         <is>
-          <t>11.13</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="Q374" t="inlineStr">
@@ -34153,20 +34177,20 @@
         </is>
       </c>
       <c r="B375" s="2" t="n">
-        <v>45248</v>
+        <v>45247</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34174,7 +34198,7 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>11.66</v>
+        <v>14</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
@@ -34183,12 +34207,12 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>20 s</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T00:45:14.508317_myrtle_4.0_Training randomised Type 2.log</t>
+          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
@@ -34203,22 +34227,22 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>GO, 11.66</t>
+          <t>GO, 14</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P375" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q375" t="inlineStr">
@@ -34244,20 +34268,20 @@
         </is>
       </c>
       <c r="B376" s="2" t="n">
-        <v>45248</v>
+        <v>45247</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34265,7 +34289,7 @@
         </is>
       </c>
       <c r="G376" t="n">
-        <v>11.66</v>
+        <v>11.73</v>
       </c>
       <c r="H376" t="inlineStr">
         <is>
@@ -34274,12 +34298,12 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>20 s</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>Experiment_2023-11-14T00:45:14.508317_myrtle_4.0_Training randomised Type 2.log</t>
+          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
@@ -34294,22 +34318,22 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>GO, 11.66</t>
+          <t>GO, 11.73</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P376" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="Q376" t="inlineStr">
@@ -34348,7 +34372,7 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34356,7 +34380,7 @@
         </is>
       </c>
       <c r="G377" t="n">
-        <v>14</v>
+        <v>11.73</v>
       </c>
       <c r="H377" t="inlineStr">
         <is>
@@ -34385,22 +34409,22 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>GO, 14</t>
+          <t>GO, 11.73</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P377" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="Q377" t="inlineStr">
@@ -34439,7 +34463,7 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34447,7 +34471,7 @@
         </is>
       </c>
       <c r="G378" t="n">
-        <v>14</v>
+        <v>12.94</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
@@ -34476,22 +34500,22 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>GO, 14</t>
+          <t>GO, 12.94</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P378" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="Q378" t="inlineStr">
@@ -34530,7 +34554,7 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34538,7 +34562,7 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>11.73</v>
+        <v>12.94</v>
       </c>
       <c r="H379" t="inlineStr">
         <is>
@@ -34567,22 +34591,22 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>GO, 11.73</t>
+          <t>GO, 12.94</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P379" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>12.94</t>
         </is>
       </c>
       <c r="Q379" t="inlineStr">
@@ -34621,19 +34645,19 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G380" t="n">
-        <v>11.73</v>
+        <v>30</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -34658,22 +34682,22 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>GO, 11.73</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P380" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="Q380" t="inlineStr">
@@ -34712,19 +34736,19 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G381" t="n">
-        <v>12.94</v>
+        <v>30</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -34749,22 +34773,22 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>GO, 12.94</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P381" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q381" t="inlineStr">
@@ -34803,19 +34827,19 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>P</t>
+          <t xml:space="preserve">N </t>
         </is>
       </c>
       <c r="G382" t="n">
-        <v>12.94</v>
+        <v>30</v>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -34840,22 +34864,22 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>GO, 12.94</t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t>ResponseCBs</t>
+          <t>TrialCBs</t>
         </is>
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>ResponseTime</t>
+          <t>ResponseType</t>
         </is>
       </c>
       <c r="P382" t="inlineStr">
         <is>
-          <t>12.94</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="Q382" t="inlineStr">
@@ -34894,7 +34918,7 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34936,17 +34960,17 @@
       </c>
       <c r="N383" t="inlineStr">
         <is>
-          <t>TrialCBs</t>
+          <t>ResponseCBs</t>
         </is>
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t>ResponseType</t>
+          <t>ResponseTime</t>
         </is>
       </c>
       <c r="P383" t="inlineStr">
         <is>
-          <t>NOGO</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q383" t="inlineStr">
@@ -34960,279 +34984,6 @@
         </is>
       </c>
       <c r="S383" t="inlineStr">
-        <is>
-          <t>NOT EQUAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>CSU</t>
-        </is>
-      </c>
-      <c r="B384" s="2" t="n">
-        <v>45247</v>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>CBF3</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>yoshi</t>
-        </is>
-      </c>
-      <c r="E384" t="n">
-        <v>12</v>
-      </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N </t>
-        </is>
-      </c>
-      <c r="G384" t="n">
-        <v>30</v>
-      </c>
-      <c r="H384" t="inlineStr">
-        <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I384" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="J384" t="inlineStr">
-        <is>
-          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
-        </is>
-      </c>
-      <c r="K384" t="inlineStr">
-        <is>
-          <t>TrialCBs, ResponseCBs</t>
-        </is>
-      </c>
-      <c r="L384" t="inlineStr">
-        <is>
-          <t>ResponseType, ResponseTime</t>
-        </is>
-      </c>
-      <c r="M384" t="inlineStr">
-        <is>
-          <t>NOGO, 30</t>
-        </is>
-      </c>
-      <c r="N384" t="inlineStr">
-        <is>
-          <t>ResponseCBs</t>
-        </is>
-      </c>
-      <c r="O384" t="inlineStr">
-        <is>
-          <t>ResponseTime</t>
-        </is>
-      </c>
-      <c r="P384" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Q384" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="R384" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="S384" t="inlineStr">
-        <is>
-          <t>NOT EQUAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>CSU</t>
-        </is>
-      </c>
-      <c r="B385" s="2" t="n">
-        <v>45247</v>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>CBF3</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>yoshi</t>
-        </is>
-      </c>
-      <c r="E385" t="n">
-        <v>20</v>
-      </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N </t>
-        </is>
-      </c>
-      <c r="G385" t="n">
-        <v>30</v>
-      </c>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I385" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="J385" t="inlineStr">
-        <is>
-          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
-        </is>
-      </c>
-      <c r="K385" t="inlineStr">
-        <is>
-          <t>TrialCBs, ResponseCBs</t>
-        </is>
-      </c>
-      <c r="L385" t="inlineStr">
-        <is>
-          <t>ResponseType, ResponseTime</t>
-        </is>
-      </c>
-      <c r="M385" t="inlineStr">
-        <is>
-          <t>NOGO, 30</t>
-        </is>
-      </c>
-      <c r="N385" t="inlineStr">
-        <is>
-          <t>TrialCBs</t>
-        </is>
-      </c>
-      <c r="O385" t="inlineStr">
-        <is>
-          <t>ResponseType</t>
-        </is>
-      </c>
-      <c r="P385" t="inlineStr">
-        <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="Q385" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="R385" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="S385" t="inlineStr">
-        <is>
-          <t>NOT EQUAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>CSU</t>
-        </is>
-      </c>
-      <c r="B386" s="2" t="n">
-        <v>45247</v>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>CBF3</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>yoshi</t>
-        </is>
-      </c>
-      <c r="E386" t="n">
-        <v>20</v>
-      </c>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N </t>
-        </is>
-      </c>
-      <c r="G386" t="n">
-        <v>30</v>
-      </c>
-      <c r="H386" t="inlineStr">
-        <is>
-          <t>NOGO</t>
-        </is>
-      </c>
-      <c r="I386" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="J386" t="inlineStr">
-        <is>
-          <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
-        </is>
-      </c>
-      <c r="K386" t="inlineStr">
-        <is>
-          <t>TrialCBs, ResponseCBs</t>
-        </is>
-      </c>
-      <c r="L386" t="inlineStr">
-        <is>
-          <t>ResponseType, ResponseTime</t>
-        </is>
-      </c>
-      <c r="M386" t="inlineStr">
-        <is>
-          <t>NOGO, 30</t>
-        </is>
-      </c>
-      <c r="N386" t="inlineStr">
-        <is>
-          <t>ResponseCBs</t>
-        </is>
-      </c>
-      <c r="O386" t="inlineStr">
-        <is>
-          <t>ResponseTime</t>
-        </is>
-      </c>
-      <c r="P386" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Q386" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="R386" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="S386" t="inlineStr">
         <is>
           <t>NOT EQUAL</t>
         </is>
